--- a/branches/migration/2026.0.0-template-v0.13.1/all-profiles.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.1/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="314">
   <si>
     <t>Property</t>
   </si>
@@ -60,10 +60,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,9 +127,6 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
     <t>Derivation</t>
   </si>
   <si>
@@ -362,9 +362,6 @@
   </si>
   <si>
     <t>true</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
   </si>
   <si>
     <t>Das Profil legt die Mindestanforderungen fest, die SearchParameter-Ressourcen im Kerndatensatz erfüllen müssen.</t>
@@ -1193,98 +1190,100 @@
       <c r="A8" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1369,94 +1368,94 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -1632,10 +1631,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
@@ -1664,7 +1663,7 @@
         <v>11</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -1715,7 +1714,7 @@
         <v>77</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>78</v>
@@ -1867,7 +1866,7 @@
         <v>90</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s" s="2">
         <v>91</v>
@@ -2147,10 +2146,10 @@
         <v>108</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
@@ -2176,13 +2175,13 @@
         <v>80</v>
       </c>
       <c r="M7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="N7" t="s" s="2">
+      <c r="O7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" t="s" s="2">
@@ -2232,7 +2231,7 @@
         <v>77</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>78</v>
@@ -2244,7 +2243,7 @@
         <v>77</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -2252,10 +2251,10 @@
         <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
@@ -2275,19 +2274,19 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="N8" t="s" s="2">
+      <c r="O8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" t="s" s="2">
@@ -2337,7 +2336,7 @@
         <v>77</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>78</v>
@@ -2357,10 +2356,10 @@
         <v>108</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
@@ -2380,16 +2379,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -2440,7 +2439,7 @@
         <v>77</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>78</v>
@@ -2460,10 +2459,10 @@
         <v>108</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
@@ -2480,22 +2479,22 @@
         <v>77</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>97</v>
       </c>
       <c r="M10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="N10" t="s" s="2">
+      <c r="O10" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" t="s" s="2">
@@ -2545,7 +2544,7 @@
         <v>77</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>78</v>
@@ -2565,10 +2564,10 @@
         <v>108</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
@@ -2591,16 +2590,16 @@
         <v>77</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" t="s" s="2">
@@ -2629,28 +2628,28 @@
         <v>105</v>
       </c>
       <c r="Z11" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AA11" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="AA11" t="s" s="2">
+      <c r="AB11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG11" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AH11" t="s" s="2">
         <v>78</v>
@@ -2670,14 +2669,14 @@
         <v>108</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" t="s" s="2">
@@ -2696,16 +2695,16 @@
         <v>77</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" t="s" s="2">
@@ -2755,7 +2754,7 @@
         <v>77</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>78</v>
@@ -2775,14 +2774,14 @@
         <v>108</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" t="s" s="2">
@@ -2801,16 +2800,16 @@
         <v>77</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" t="s" s="2">
@@ -2860,7 +2859,7 @@
         <v>77</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>78</v>
@@ -2880,14 +2879,14 @@
         <v>108</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" t="s" s="2">
@@ -2909,13 +2908,13 @@
         <v>90</v>
       </c>
       <c r="M14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" t="s" s="2">
@@ -2965,7 +2964,7 @@
         <v>77</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>78</v>
@@ -2985,14 +2984,14 @@
         <v>108</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" t="s" s="2">
@@ -3005,7 +3004,7 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>77</v>
@@ -3014,16 +3013,16 @@
         <v>90</v>
       </c>
       <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="P15" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="P15" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="Q15" t="s" s="2">
         <v>77</v>
@@ -3072,7 +3071,7 @@
         <v>77</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>78</v>
@@ -3092,10 +3091,10 @@
         <v>108</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -3115,22 +3114,22 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>97</v>
       </c>
       <c r="M16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O16" t="s" s="2">
+      <c r="P16" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="P16" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="Q16" t="s" s="2">
         <v>77</v>
@@ -3179,7 +3178,7 @@
         <v>77</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>84</v>
@@ -3199,10 +3198,10 @@
         <v>108</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3222,19 +3221,19 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>85</v>
       </c>
       <c r="M17" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" t="s" s="2">
@@ -3284,7 +3283,7 @@
         <v>77</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>78</v>
@@ -3304,10 +3303,10 @@
         <v>108</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -3327,22 +3326,22 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>85</v>
       </c>
       <c r="M18" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="O18" t="s" s="2">
+      <c r="P18" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="P18" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="Q18" t="s" s="2">
         <v>77</v>
@@ -3391,7 +3390,7 @@
         <v>77</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>84</v>
@@ -3400,7 +3399,7 @@
         <v>84</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>107</v>
@@ -3411,10 +3410,10 @@
         <v>108</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
@@ -3437,16 +3436,16 @@
         <v>77</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
@@ -3496,7 +3495,7 @@
         <v>77</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>78</v>
@@ -3516,10 +3515,10 @@
         <v>108</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -3536,22 +3535,22 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
@@ -3577,14 +3576,14 @@
         <v>77</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z20" t="s" s="2">
+      <c r="AA20" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AA20" t="s" s="2">
-        <v>198</v>
-      </c>
       <c r="AB20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3601,7 +3600,7 @@
         <v>77</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>84</v>
@@ -3621,10 +3620,10 @@
         <v>108</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -3644,22 +3643,22 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="P21" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="Q21" t="s" s="2">
         <v>77</v>
@@ -3708,7 +3707,7 @@
         <v>77</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>78</v>
@@ -3728,14 +3727,14 @@
         <v>108</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
@@ -3751,19 +3750,19 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
@@ -3813,7 +3812,7 @@
         <v>77</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>78</v>
@@ -3833,10 +3832,10 @@
         <v>108</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -3856,22 +3855,22 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="O23" t="s" s="2">
+      <c r="P23" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="P23" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="Q23" t="s" s="2">
         <v>77</v>
@@ -3920,7 +3919,7 @@
         <v>77</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>78</v>
@@ -3940,10 +3939,10 @@
         <v>108</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -3963,19 +3962,19 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" t="s" s="2">
@@ -4025,7 +4024,7 @@
         <v>77</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>78</v>
@@ -4045,10 +4044,10 @@
         <v>108</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4068,19 +4067,19 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
@@ -4130,7 +4129,7 @@
         <v>77</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>84</v>
@@ -4150,10 +4149,10 @@
         <v>108</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4173,22 +4172,22 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="O26" t="s" s="2">
+      <c r="P26" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="P26" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="Q26" t="s" s="2">
         <v>77</v>
@@ -4237,7 +4236,7 @@
         <v>77</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>78</v>
@@ -4257,10 +4256,10 @@
         <v>108</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -4280,19 +4279,19 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>102</v>
       </c>
       <c r="M27" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" t="s" s="2">
@@ -4318,14 +4317,14 @@
         <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AA27" t="s" s="2">
-        <v>237</v>
-      </c>
       <c r="AB27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4342,7 +4341,7 @@
         <v>77</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>78</v>
@@ -4362,10 +4361,10 @@
         <v>108</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -4388,16 +4387,16 @@
         <v>77</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M28" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
@@ -4447,7 +4446,7 @@
         <v>77</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
@@ -4467,10 +4466,10 @@
         <v>108</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4490,19 +4489,19 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M29" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
@@ -4552,7 +4551,7 @@
         <v>77</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>84</v>
@@ -4564,7 +4563,7 @@
         <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
@@ -4572,10 +4571,10 @@
         <v>108</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4595,19 +4594,19 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
@@ -4633,14 +4632,14 @@
         <v>77</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Z30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AA30" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AA30" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AB30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4657,7 +4656,7 @@
         <v>77</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>84</v>
@@ -4677,10 +4676,10 @@
         <v>108</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -4700,16 +4699,16 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M31" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -4736,14 +4735,14 @@
         <v>77</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Z31" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AA31" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AA31" t="s" s="2">
-        <v>257</v>
-      </c>
       <c r="AB31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4760,7 +4759,7 @@
         <v>77</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>84</v>
@@ -4780,10 +4779,10 @@
         <v>108</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -4809,13 +4808,13 @@
         <v>85</v>
       </c>
       <c r="M32" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
@@ -4865,7 +4864,7 @@
         <v>77</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>78</v>
@@ -4874,7 +4873,7 @@
         <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>107</v>
@@ -4885,10 +4884,10 @@
         <v>108</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -4914,13 +4913,13 @@
         <v>85</v>
       </c>
       <c r="M33" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
@@ -4970,7 +4969,7 @@
         <v>77</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>78</v>
@@ -4979,7 +4978,7 @@
         <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>107</v>
@@ -4990,10 +4989,10 @@
         <v>108</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5016,13 +5015,13 @@
         <v>77</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M34" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -5049,14 +5048,14 @@
         <v>77</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Z34" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AA34" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AA34" t="s" s="2">
-        <v>271</v>
-      </c>
       <c r="AB34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5073,7 +5072,7 @@
         <v>77</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>78</v>
@@ -5082,7 +5081,7 @@
         <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>107</v>
@@ -5093,10 +5092,10 @@
         <v>108</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5119,13 +5118,13 @@
         <v>77</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -5152,14 +5151,14 @@
         <v>77</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Z35" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AA35" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AB35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5176,7 +5175,7 @@
         <v>77</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>78</v>
@@ -5196,10 +5195,10 @@
         <v>108</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5222,13 +5221,13 @@
         <v>77</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -5279,7 +5278,7 @@
         <v>77</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>78</v>
@@ -5299,10 +5298,10 @@
         <v>108</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5325,13 +5324,13 @@
         <v>77</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -5382,7 +5381,7 @@
         <v>77</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>78</v>
@@ -5402,10 +5401,10 @@
         <v>108</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5428,16 +5427,16 @@
         <v>77</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M38" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" t="s" s="2">
@@ -5463,14 +5462,14 @@
         <v>77</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AA38" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="AB38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5487,7 +5486,7 @@
         <v>77</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>78</v>
@@ -5507,10 +5506,10 @@
         <v>108</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -5533,13 +5532,13 @@
         <v>77</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -5566,14 +5565,14 @@
         <v>77</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Z39" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AA39" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AA39" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AB39" t="s" s="2">
         <v>77</v>
       </c>
@@ -5590,7 +5589,7 @@
         <v>77</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>78</v>
@@ -5610,10 +5609,10 @@
         <v>108</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -5639,13 +5638,13 @@
         <v>85</v>
       </c>
       <c r="M40" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" t="s" s="2">
@@ -5695,7 +5694,7 @@
         <v>77</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>78</v>
@@ -5715,10 +5714,10 @@
         <v>108</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -5741,13 +5740,13 @@
         <v>77</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -5798,7 +5797,7 @@
         <v>77</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>78</v>
@@ -5818,10 +5817,10 @@
         <v>108</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -5921,14 +5920,14 @@
         <v>108</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
@@ -5950,13 +5949,13 @@
         <v>90</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
@@ -6026,14 +6025,14 @@
         <v>108</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
@@ -6046,25 +6045,25 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>90</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>306</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q44" t="s" s="2">
         <v>77</v>
@@ -6113,7 +6112,7 @@
         <v>77</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>78</v>
@@ -6133,10 +6132,10 @@
         <v>108</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6159,13 +6158,13 @@
         <v>77</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -6216,7 +6215,7 @@
         <v>77</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>84</v>
@@ -6236,10 +6235,10 @@
         <v>108</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6265,13 +6264,13 @@
         <v>85</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -6321,7 +6320,7 @@
         <v>77</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>84</v>
